--- a/schoolDocs/Class4_ImportReady.xlsx
+++ b/schoolDocs/Class4_ImportReady.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="135">
   <si>
     <t>Sr No</t>
   </si>
@@ -50,6 +50,9 @@
     <t>Already Collected (Rs)</t>
   </si>
   <si>
+    <t>Admission Date (DD/MM/YYYY)</t>
+  </si>
+  <si>
     <t>Village</t>
   </si>
   <si>
@@ -92,6 +95,9 @@
     <t>general</t>
   </si>
   <si>
+    <t>21/01/2020</t>
+  </si>
+  <si>
     <t>Boripardhi</t>
   </si>
   <si>
@@ -107,6 +113,9 @@
     <t>Vansh Ughade</t>
   </si>
   <si>
+    <t>04/01/2020</t>
+  </si>
+  <si>
     <t>Kedgaon</t>
   </si>
   <si>
@@ -122,6 +131,9 @@
     <t>Rajvir Dhaygude</t>
   </si>
   <si>
+    <t>02/01/2022</t>
+  </si>
+  <si>
     <t>Chaufula</t>
   </si>
   <si>
@@ -134,12 +146,18 @@
     <t>Godwin Pappachan Reji</t>
   </si>
   <si>
+    <t>28/01/2020</t>
+  </si>
+  <si>
     <t>Tyre Shop</t>
   </si>
   <si>
     <t>Punit Ingle</t>
   </si>
   <si>
+    <t>13/02/2020</t>
+  </si>
+  <si>
     <t>Vakdapul</t>
   </si>
   <si>
@@ -152,6 +170,9 @@
     <t>Viraj Gorgal</t>
   </si>
   <si>
+    <t>02/02/2020</t>
+  </si>
+  <si>
     <t>Security Guard</t>
   </si>
   <si>
@@ -167,12 +188,18 @@
     <t>rte</t>
   </si>
   <si>
+    <t>20/01/2022</t>
+  </si>
+  <si>
     <t>RTE — fees paid by government</t>
   </si>
   <si>
     <t>Sairaj Memane</t>
   </si>
   <si>
+    <t>05/02/2020</t>
+  </si>
+  <si>
     <t>Varvand</t>
   </si>
   <si>
@@ -188,13 +215,16 @@
     <t>discount</t>
   </si>
   <si>
+    <t>22/12/2021</t>
+  </si>
+  <si>
     <t>Discount 25% on boys fee ₹16200 = ₹12150 payable — full paid</t>
   </si>
   <si>
     <t>Aryan Chaurasiya</t>
   </si>
   <si>
-    <t>DGA G=0.5 (50%) but total ₹8000 — 50% of ₹16200 = ₹8100. Using ₹8000 as custom fee. Please verify.</t>
+    <t>DGA G=0.5 (50%) but total ₹8000 — using ₹8000 as custom fee. Please verify.</t>
   </si>
   <si>
     <t>Viraj Kshirsagar</t>
@@ -203,6 +233,9 @@
     <t>coc</t>
   </si>
   <si>
+    <t>26/12/2019</t>
+  </si>
+  <si>
     <t>Kasurdi</t>
   </si>
   <si>
@@ -215,18 +248,27 @@
     <t>Adil Shaikh</t>
   </si>
   <si>
+    <t>01/12/2019</t>
+  </si>
+  <si>
     <t>CoC student — full ₹16200 collected</t>
   </si>
   <si>
     <t>Sahil Kashid</t>
   </si>
   <si>
+    <t>25/12/2021</t>
+  </si>
+  <si>
     <t>DGA shows ₹12200 for this CoC boy — system will use ₹16200. Please verify.</t>
   </si>
   <si>
     <t>Prathmesh Bhosale</t>
   </si>
   <si>
+    <t>03/01/2022</t>
+  </si>
+  <si>
     <t>Road seller</t>
   </si>
   <si>
@@ -239,9 +281,15 @@
     <t>female</t>
   </si>
   <si>
+    <t>24/12/2019</t>
+  </si>
+  <si>
     <t>Aliya Ansari</t>
   </si>
   <si>
+    <t>29/01/2020</t>
+  </si>
+  <si>
     <t>Works at Bakery Shop</t>
   </si>
   <si>
@@ -251,15 +299,21 @@
     <t>Anushka Shinge</t>
   </si>
   <si>
+    <t>17/12/2019</t>
+  </si>
+  <si>
     <t>Chef</t>
   </si>
   <si>
-    <t>Contact in DGA sheet was 9 digits (invalid) — left blank</t>
+    <t>Contact in DGA was 9 digits (invalid) — left blank</t>
   </si>
   <si>
     <t>Swara Ghogare</t>
   </si>
   <si>
+    <t>18/12/2019</t>
+  </si>
+  <si>
     <t>Labour</t>
   </si>
   <si>
@@ -275,15 +329,24 @@
     <t>Sanam Tamboli</t>
   </si>
   <si>
+    <t>05/12/2019</t>
+  </si>
+  <si>
     <t>Chicken Shop</t>
   </si>
   <si>
     <t>Mahira Ansari</t>
   </si>
   <si>
+    <t>12/02/2020</t>
+  </si>
+  <si>
     <t>Kanchan Kolape</t>
   </si>
   <si>
+    <t>28/12/2019</t>
+  </si>
+  <si>
     <t>Keskar vasti</t>
   </si>
   <si>
@@ -302,6 +365,9 @@
     <t>Pranjal Baravkar</t>
   </si>
   <si>
+    <t>03/12/2019</t>
+  </si>
+  <si>
     <t>General store</t>
   </si>
   <si>
@@ -311,6 +377,9 @@
     <t>Aarohi Aade</t>
   </si>
   <si>
+    <t>09/12/2019</t>
+  </si>
+  <si>
     <t>Bhandgaon</t>
   </si>
   <si>
@@ -323,6 +392,9 @@
     <t>Archana Gaikwad</t>
   </si>
   <si>
+    <t>10/02/2020</t>
+  </si>
+  <si>
     <t>Yawat</t>
   </si>
   <si>
@@ -338,10 +410,16 @@
     <t>Richa Awasare</t>
   </si>
   <si>
+    <t>13/12/2021</t>
+  </si>
+  <si>
     <t>Discount 25% on girls ₹12200 = ₹9150 payable — collected ₹6100 (partial)</t>
   </si>
   <si>
     <t>Aarju Sayyad</t>
+  </si>
+  <si>
+    <t>04/02/2020</t>
   </si>
 </sst>
 </file>
@@ -378,7 +456,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -403,6 +481,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EAD0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -416,7 +500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
@@ -425,6 +509,9 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
@@ -727,7 +814,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
@@ -741,18 +828,19 @@
     <col min="9" max="9" width="15.139" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="24.565" bestFit="true" customWidth="true" style="0"/>
     <col min="11" max="11" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="25.851" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="116.686" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="35.277" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="16.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="25.851" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="16.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="28.136" bestFit="true" customWidth="true" style="0"/>
+    <col min="19" max="19" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="21" max="21" width="89.55" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" customHeight="1" ht="30">
+    <row r="1" spans="1:21" customHeight="1" ht="30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -786,7 +874,7 @@
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -810,346 +898,376 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20">
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K2">
         <v>16200</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="N2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:20">
+      <c r="P2" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3">
         <v>9967125742</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="4">
+        <v>25</v>
+      </c>
+      <c r="K3" s="5">
         <v>5000</v>
       </c>
       <c r="L3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" spans="1:20">
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4">
         <v>9766876363</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K4">
         <v>16200</v>
       </c>
       <c r="L4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M4" t="s">
-        <v>36</v>
-      </c>
-      <c r="O4" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" t="s">
+        <v>41</v>
+      </c>
+      <c r="R4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5">
         <v>9373238576</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5" t="s">
         <v>30</v>
       </c>
-      <c r="M5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
-      </c>
-      <c r="O6" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="N6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P6" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K7">
         <v>16200</v>
       </c>
       <c r="L7" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" t="s">
+        <v>52</v>
+      </c>
+      <c r="R7" t="s">
         <v>30</v>
       </c>
-      <c r="M7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8">
         <v>8390635894</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M8" t="s">
-        <v>36</v>
-      </c>
-      <c r="O8" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
+        <v>39</v>
+      </c>
+      <c r="N8" t="s">
+        <v>40</v>
+      </c>
+      <c r="P8" t="s">
+        <v>54</v>
+      </c>
+      <c r="R8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G9">
         <v>9730004940</v>
       </c>
       <c r="H9" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L9" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
-      </c>
-      <c r="T9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
+        <v>33</v>
+      </c>
+      <c r="N9" t="s">
+        <v>28</v>
+      </c>
+      <c r="U9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10">
         <v>7887895321</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="M10" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
+        <v>61</v>
+      </c>
+      <c r="N10" t="s">
+        <v>62</v>
+      </c>
+      <c r="R10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G11">
         <v>8485054355</v>
       </c>
       <c r="H11" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="I11">
         <v>25</v>
@@ -1158,36 +1276,39 @@
         <v>12150</v>
       </c>
       <c r="L11" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="M11" t="s">
-        <v>36</v>
-      </c>
-      <c r="T11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
+        <v>39</v>
+      </c>
+      <c r="N11" t="s">
+        <v>40</v>
+      </c>
+      <c r="U11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G12">
         <v>8545074211</v>
       </c>
       <c r="H12" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J12">
         <v>8000</v>
@@ -1196,310 +1317,337 @@
         <v>8000</v>
       </c>
       <c r="L12" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="M12" t="s">
-        <v>42</v>
-      </c>
-      <c r="O12" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>28</v>
-      </c>
-      <c r="T12" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="N12" t="s">
+        <v>48</v>
+      </c>
+      <c r="P12" t="s">
+        <v>49</v>
+      </c>
+      <c r="R12" t="s">
+        <v>30</v>
+      </c>
+      <c r="U12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L13" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="M13" t="s">
-        <v>63</v>
-      </c>
-      <c r="T13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
+        <v>73</v>
+      </c>
+      <c r="N13" t="s">
+        <v>74</v>
+      </c>
+      <c r="U13" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K14">
         <v>16200</v>
       </c>
-      <c r="T14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+      <c r="L14" t="s">
+        <v>77</v>
+      </c>
+      <c r="U14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K15">
         <v>12200</v>
       </c>
-      <c r="T15" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
+      <c r="L15" t="s">
+        <v>80</v>
+      </c>
+      <c r="U15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G16">
         <v>9766444535</v>
       </c>
       <c r="H16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L16" t="s">
+        <v>83</v>
+      </c>
+      <c r="M16" t="s">
+        <v>33</v>
+      </c>
+      <c r="N16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" t="s">
+        <v>84</v>
+      </c>
+      <c r="R16" t="s">
         <v>30</v>
       </c>
-      <c r="M16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O16" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>28</v>
-      </c>
-      <c r="T16" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
+      <c r="U16" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17">
         <v>9960184120</v>
       </c>
       <c r="H17" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L17" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="M17" t="s">
-        <v>26</v>
-      </c>
-      <c r="T17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+        <v>27</v>
+      </c>
+      <c r="N17" t="s">
+        <v>28</v>
+      </c>
+      <c r="U17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H18" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="I18">
         <v>25</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18">
         <v>3150</v>
       </c>
       <c r="L18" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="M18" t="s">
-        <v>36</v>
-      </c>
-      <c r="O18" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>28</v>
-      </c>
-      <c r="T18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+        <v>39</v>
+      </c>
+      <c r="N18" t="s">
+        <v>40</v>
+      </c>
+      <c r="P18" t="s">
+        <v>91</v>
+      </c>
+      <c r="R18" t="s">
+        <v>30</v>
+      </c>
+      <c r="U18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K19">
         <v>12200</v>
       </c>
       <c r="L19" t="s">
+        <v>94</v>
+      </c>
+      <c r="M19" t="s">
+        <v>33</v>
+      </c>
+      <c r="N19" t="s">
+        <v>28</v>
+      </c>
+      <c r="P19" t="s">
+        <v>95</v>
+      </c>
+      <c r="R19" t="s">
         <v>30</v>
       </c>
-      <c r="M19" t="s">
-        <v>26</v>
-      </c>
-      <c r="O19" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>28</v>
-      </c>
-      <c r="T19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+      <c r="U19" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G20">
         <v>9823827707</v>
       </c>
       <c r="H20" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="I20">
         <v>25</v>
       </c>
       <c r="L20" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="M20" t="s">
-        <v>42</v>
-      </c>
-      <c r="O20" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>28</v>
-      </c>
-      <c r="T20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
+        <v>39</v>
+      </c>
+      <c r="N20" t="s">
+        <v>48</v>
+      </c>
+      <c r="P20" t="s">
+        <v>99</v>
+      </c>
+      <c r="R20" t="s">
+        <v>30</v>
+      </c>
+      <c r="U20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="I21">
         <v>25</v>
@@ -1508,77 +1656,83 @@
         <v>9150</v>
       </c>
       <c r="L21" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="M21" t="s">
-        <v>42</v>
-      </c>
-      <c r="O21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>28</v>
-      </c>
-      <c r="T21" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
+        <v>47</v>
+      </c>
+      <c r="N21" t="s">
+        <v>48</v>
+      </c>
+      <c r="P21" t="s">
+        <v>49</v>
+      </c>
+      <c r="R21" t="s">
+        <v>30</v>
+      </c>
+      <c r="U21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="I22">
         <v>25</v>
       </c>
       <c r="L22" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="M22" t="s">
-        <v>36</v>
-      </c>
-      <c r="O22" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>28</v>
-      </c>
-      <c r="T22" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+        <v>39</v>
+      </c>
+      <c r="N22" t="s">
+        <v>40</v>
+      </c>
+      <c r="P22" t="s">
+        <v>105</v>
+      </c>
+      <c r="R22" t="s">
+        <v>30</v>
+      </c>
+      <c r="U22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" t="s">
         <v>87</v>
       </c>
-      <c r="D23" t="s">
-        <v>73</v>
-      </c>
       <c r="E23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="I23">
         <v>25</v>
@@ -1587,165 +1741,177 @@
         <v>9150</v>
       </c>
       <c r="L23" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="M23" t="s">
-        <v>36</v>
-      </c>
-      <c r="O23" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>28</v>
-      </c>
-      <c r="T23" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+        <v>39</v>
+      </c>
+      <c r="N23" t="s">
+        <v>40</v>
+      </c>
+      <c r="P23" t="s">
+        <v>91</v>
+      </c>
+      <c r="R23" t="s">
+        <v>30</v>
+      </c>
+      <c r="U23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K24">
         <v>8200</v>
       </c>
       <c r="L24" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="M24" t="s">
-        <v>90</v>
-      </c>
-      <c r="O24" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>92</v>
-      </c>
-      <c r="T24" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
+        <v>110</v>
+      </c>
+      <c r="N24" t="s">
+        <v>111</v>
+      </c>
+      <c r="P24" t="s">
+        <v>112</v>
+      </c>
+      <c r="R24" t="s">
+        <v>113</v>
+      </c>
+      <c r="U24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="I25">
         <v>25</v>
       </c>
-      <c r="K25" s="4">
+      <c r="K25">
         <v>4100</v>
       </c>
       <c r="L25" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="M25" t="s">
-        <v>36</v>
-      </c>
-      <c r="O25" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>95</v>
-      </c>
-      <c r="T25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20">
+        <v>39</v>
+      </c>
+      <c r="N25" t="s">
+        <v>40</v>
+      </c>
+      <c r="P25" t="s">
+        <v>117</v>
+      </c>
+      <c r="R25" t="s">
+        <v>117</v>
+      </c>
+      <c r="U25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26">
         <v>7709642604</v>
       </c>
       <c r="H26" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J26">
         <v>11000</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="5">
         <v>11000</v>
       </c>
       <c r="L26" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="M26" t="s">
-        <v>26</v>
-      </c>
-      <c r="O26" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q26" t="s">
+        <v>121</v>
+      </c>
+      <c r="N26" t="s">
         <v>28</v>
       </c>
-      <c r="T26" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20">
+      <c r="P26" t="s">
+        <v>122</v>
+      </c>
+      <c r="R26" t="s">
+        <v>30</v>
+      </c>
+      <c r="U26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G27">
         <v>8788402403</v>
       </c>
       <c r="H27" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J27">
         <v>10000</v>
@@ -1754,118 +1920,131 @@
         <v>10000</v>
       </c>
       <c r="L27" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="M27" t="s">
-        <v>103</v>
-      </c>
-      <c r="T27" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20">
+        <v>126</v>
+      </c>
+      <c r="N27" t="s">
+        <v>127</v>
+      </c>
+      <c r="U27" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L28" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="M28" t="s">
-        <v>26</v>
-      </c>
-      <c r="O28" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20">
+        <v>27</v>
+      </c>
+      <c r="N28" t="s">
+        <v>28</v>
+      </c>
+      <c r="P28" t="s">
+        <v>122</v>
+      </c>
+      <c r="R28" t="s">
+        <v>122</v>
+      </c>
+      <c r="U28" s="5"/>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H29" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="I29">
         <v>25</v>
       </c>
-      <c r="K29" s="4">
+      <c r="K29">
         <v>6100</v>
       </c>
       <c r="L29" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="M29" t="s">
-        <v>26</v>
-      </c>
-      <c r="T29" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
+        <v>27</v>
+      </c>
+      <c r="N29" t="s">
+        <v>28</v>
+      </c>
+      <c r="U29" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G30">
         <v>7822936079</v>
       </c>
       <c r="H30" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L30" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="M30" t="s">
-        <v>103</v>
-      </c>
-      <c r="O30" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>99</v>
-      </c>
-      <c r="T30" t="s">
-        <v>50</v>
+        <v>126</v>
+      </c>
+      <c r="N30" t="s">
+        <v>127</v>
+      </c>
+      <c r="P30" t="s">
+        <v>122</v>
+      </c>
+      <c r="R30" t="s">
+        <v>122</v>
+      </c>
+      <c r="U30" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
